--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_45.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3939309.735946483</v>
+        <v>3975639.950431578</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>987.0883260126807</v>
+        <v>987.0883260128377</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>987.0883260126807</v>
+        <v>987.0883260128377</v>
       </c>
     </row>
     <row r="11">
@@ -666,10 +666,10 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>4.889628708012481</v>
       </c>
       <c r="G2" t="n">
-        <v>1.415908396048882</v>
+        <v>1.415908396048256</v>
       </c>
       <c r="H2" t="n">
         <v>3.769060713577687</v>
@@ -742,19 +742,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>40.18239206839011</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -790,16 +790,16 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>114.4356662753492</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
-        <v>373</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>373</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.343301935257416</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>5.722467174369151</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.41253966161939</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8629887637398</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.18817092047</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>119.2370946515431</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>133.5184388018133</v>
+        <v>374</v>
       </c>
       <c r="S6" t="n">
-        <v>62.44885845517734</v>
+        <v>170.4054287048467</v>
       </c>
       <c r="T6" t="n">
-        <v>4.46477465147608</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886345</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.51638189435316</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
         <v>142.7621408454554</v>
@@ -1091,7 +1091,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>264.9837661807365</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
         <v>310.286266425598</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.343301935257416</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577661</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.953406460791602</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161939</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8629887637398</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.18817092047</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,16 +1213,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018133</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
         <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.46477465147608</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>170.9507451188515</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>357.7944651142078</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.51638189435316</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
         <v>142.7621408454554</v>
@@ -1328,7 +1328,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>264.9837661807365</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
         <v>310.286266425598</v>
@@ -1380,7 +1380,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.83504507946625</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1447,22 +1447,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>213.6917283274924</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>98.98524175149981</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,19 +1489,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1565,13 +1565,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
         <v>30.56285675203577</v>
@@ -1620,7 +1620,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>142.3350019731772</v>
@@ -1690,19 +1690,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>324.61299891065</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H15" t="n">
         <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>252.7534963968768</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
@@ -1796,7 +1796,7 @@
         <v>102.3923982877958</v>
       </c>
       <c r="N16" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O16" t="n">
         <v>231.765039488851</v>
@@ -1811,7 +1811,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,13 +1854,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H17" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1921,25 +1921,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I18" t="n">
-        <v>173.5918158819728</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1969,25 +1969,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T18" t="n">
-        <v>81.3753501231742</v>
+        <v>254.9671660051473</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2039,16 +2039,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P19" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q19" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2158,13 +2158,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09991244551929</v>
+        <v>135.063180218145</v>
       </c>
       <c r="D21" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>18.63624233787687</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
         <v>180.333570877285</v>
@@ -2215,7 +2215,7 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V21" t="n">
-        <v>267.1024830734931</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
         <v>432.3731429098285</v>
@@ -2224,7 +2224,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2273,7 +2273,7 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O22" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
         <v>291.4220612627038</v>
@@ -2285,7 +2285,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>177.5914272286988</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,25 +2440,25 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>284.9649587918016</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2501,25 +2501,25 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N25" t="n">
         <v>155.2579933044718</v>
       </c>
       <c r="O25" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
         <v>30.56285675203577</v>
@@ -2571,7 +2571,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2638,16 +2638,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H27" t="n">
-        <v>325.021973978874</v>
+        <v>98.98524175149959</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
         <v>180.333570877285</v>
@@ -2695,10 +2695,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>272.4545553273608</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N28" t="n">
         <v>155.2579933044718</v>
@@ -2802,7 +2802,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
@@ -2869,7 +2869,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>40.09991244551929</v>
+        <v>135.063180218145</v>
       </c>
       <c r="D30" t="n">
         <v>26.93768689770263</v>
@@ -2881,10 +2881,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H30" t="n">
-        <v>177.6137898608472</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,25 +2911,25 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>98.86273944538755</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2987,13 +2987,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H32" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3115,16 +3115,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873961</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I33" t="n">
-        <v>173.591815881973</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,28 +3148,28 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>180.333570877285</v>
+        <v>275.2968386499108</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V33" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M34" t="n">
         <v>102.3923982877958</v>
@@ -3224,16 +3224,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S34" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3343,16 +3343,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>213.6917283274924</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
         <v>3.999611346725456</v>
@@ -3388,19 +3388,19 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490372</v>
+        <v>252.7534963968771</v>
       </c>
       <c r="V36" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>111.3731429098285</v>
@@ -3580,13 +3580,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>213.6917283274924</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
-        <v>180.333570877285</v>
+        <v>275.2968386499106</v>
       </c>
       <c r="S39" t="n">
         <v>131.8202263797056</v>
@@ -3750,10 +3750,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949504</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>174.1249482875295</v>
+        <v>252.7534963968773</v>
       </c>
       <c r="V42" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4054,7 +4054,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>26.93768689770263</v>
@@ -4066,13 +4066,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4102,13 +4102,13 @@
         <v>501.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>434.7611280684435</v>
+        <v>305.412042261679</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4309,7 +4309,7 @@
         <v>40.016361431958</v>
       </c>
       <c r="F2" t="n">
-        <v>35.07734253497633</v>
+        <v>35.0773425349757</v>
       </c>
       <c r="G2" t="n">
         <v>33.64713203391685</v>
@@ -4324,22 +4324,22 @@
         <v>399.11</v>
       </c>
       <c r="K2" t="n">
-        <v>451.2545884924623</v>
+        <v>768.3799999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>515.9445614572863</v>
+        <v>833.069972964824</v>
       </c>
       <c r="M2" t="n">
-        <v>885.2145614572864</v>
+        <v>1202.339972964824</v>
       </c>
       <c r="N2" t="n">
-        <v>1254.484561457286</v>
+        <v>1202.339972964824</v>
       </c>
       <c r="O2" t="n">
-        <v>1254.484561457286</v>
+        <v>1202.339972964824</v>
       </c>
       <c r="P2" t="n">
-        <v>1313.148767846158</v>
+        <v>1261.004179353695</v>
       </c>
       <c r="Q2" t="n">
         <v>1492</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.454702729969</v>
+        <v>1075.663263689516</v>
       </c>
       <c r="C3" t="n">
-        <v>241.454702729969</v>
+        <v>1075.663263689516</v>
       </c>
       <c r="D3" t="n">
-        <v>241.454702729969</v>
+        <v>1075.663263689516</v>
       </c>
       <c r="E3" t="n">
-        <v>241.454702729969</v>
+        <v>1035.074988872961</v>
       </c>
       <c r="F3" t="n">
-        <v>241.454702729969</v>
+        <v>692.0080774205599</v>
       </c>
       <c r="G3" t="n">
-        <v>241.454702729969</v>
+        <v>363.2020282233719</v>
       </c>
       <c r="H3" t="n">
-        <v>241.454702729969</v>
+        <v>29.84</v>
       </c>
       <c r="I3" t="n">
         <v>29.84</v>
@@ -4406,46 +4406,46 @@
         <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>714.3818833454045</v>
+        <v>714.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>856.0360750882637</v>
+        <v>856.0360750882628</v>
       </c>
       <c r="N3" t="n">
         <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1337.587921002192</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1492.000000000001</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1345.738421006377</v>
+        <v>1345.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1210.871311105556</v>
+        <v>1210.871311105555</v>
       </c>
       <c r="S3" t="n">
         <v>1147.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>1143.281782714997</v>
+        <v>1143.281782714996</v>
       </c>
       <c r="U3" t="n">
-        <v>1027.690200618685</v>
+        <v>1143.084020807432</v>
       </c>
       <c r="V3" t="n">
-        <v>650.9225238510079</v>
+        <v>1128.426781220038</v>
       </c>
       <c r="W3" t="n">
-        <v>618.2223794976458</v>
+        <v>1095.726636866676</v>
       </c>
       <c r="X3" t="n">
-        <v>241.454702729969</v>
+        <v>1075.663263689516</v>
       </c>
       <c r="Y3" t="n">
-        <v>241.454702729969</v>
+        <v>1075.663263689516</v>
       </c>
     </row>
     <row r="4">
@@ -4455,22 +4455,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>431.0470556274095</v>
+        <v>364.7202581567789</v>
       </c>
       <c r="C4" t="n">
-        <v>557.0490614458453</v>
+        <v>364.7202581567789</v>
       </c>
       <c r="D4" t="n">
-        <v>557.0490614458453</v>
+        <v>364.7202581567789</v>
       </c>
       <c r="E4" t="n">
-        <v>557.0490614458453</v>
+        <v>482.5491623681919</v>
       </c>
       <c r="F4" t="n">
-        <v>557.0490614458453</v>
+        <v>482.5491623681919</v>
       </c>
       <c r="G4" t="n">
-        <v>557.0490614458453</v>
+        <v>482.5491623681919</v>
       </c>
       <c r="H4" t="n">
         <v>653.700610806278</v>
@@ -4518,13 +4518,13 @@
         <v>259.1561373677321</v>
       </c>
       <c r="W4" t="n">
-        <v>431.0470556274095</v>
+        <v>259.1561373677321</v>
       </c>
       <c r="X4" t="n">
-        <v>431.0470556274095</v>
+        <v>259.1561373677321</v>
       </c>
       <c r="Y4" t="n">
-        <v>431.0470556274095</v>
+        <v>259.1561373677321</v>
       </c>
     </row>
     <row r="5">
@@ -4549,25 +4549,25 @@
         <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>35.70026987310015</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>30.01969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>82.16427879223495</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>326.5557936111288</v>
+        <v>835.1299729648241</v>
       </c>
       <c r="M5" t="n">
-        <v>696.8157936111288</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N5" t="n">
         <v>1067.075793611129</v>
@@ -4658,31 +4658,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1375.358575619502</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1240.491465718681</v>
+        <v>971.7607285971344</v>
       </c>
       <c r="S6" t="n">
-        <v>1177.411810713451</v>
+        <v>799.6340329356731</v>
       </c>
       <c r="T6" t="n">
-        <v>1172.901937328121</v>
+        <v>795.1241595503437</v>
       </c>
       <c r="U6" t="n">
-        <v>1172.704175420557</v>
+        <v>794.9263976427794</v>
       </c>
       <c r="V6" t="n">
-        <v>1158.046935833163</v>
+        <v>780.2691580553853</v>
       </c>
       <c r="W6" t="n">
-        <v>1125.346791479801</v>
+        <v>747.5690137020232</v>
       </c>
       <c r="X6" t="n">
-        <v>1105.283418302642</v>
+        <v>727.505640524864</v>
       </c>
       <c r="Y6" t="n">
-        <v>1105.283418302642</v>
+        <v>727.505640524864</v>
       </c>
     </row>
     <row r="7">
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1250.707100357225</v>
+        <v>1210.252312640102</v>
       </c>
       <c r="C7" t="n">
-        <v>1376.709106175661</v>
+        <v>1336.254318458537</v>
       </c>
       <c r="D7" t="n">
         <v>1385.467095409585</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.37478771712394</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>259.2361373677321</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7973598420842</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="V7" t="n">
-        <v>704.6187527280301</v>
+        <v>664.1639650109064</v>
       </c>
       <c r="W7" t="n">
-        <v>876.5096709877075</v>
+        <v>836.0548832705838</v>
       </c>
       <c r="X7" t="n">
-        <v>1027.540462011901</v>
+        <v>987.0856742947773</v>
       </c>
       <c r="Y7" t="n">
-        <v>1138.949762690933</v>
+        <v>1098.49497497381</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.8684999460195</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>56.89417848844987</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>46.45058683203594</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>42.04322359277468</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>37.10420469579301</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391683</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>30.01969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>82.16427879223495</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>326.5557936111288</v>
+        <v>1140.7</v>
       </c>
       <c r="M8" t="n">
-        <v>696.8157936111288</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.026862160817</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.751569573322</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.021277892777</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3160547407873</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1433030571268</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>496.3620141874828</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1379399847881</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6960887900341</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1053.245169637167</v>
+        <v>29.92</v>
       </c>
       <c r="C9" t="n">
-        <v>1053.245169637167</v>
+        <v>29.92</v>
       </c>
       <c r="D9" t="n">
-        <v>701.7929606495888</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>701.7929606495888</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>358.7260491971879</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1495.800085368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R9" t="n">
-        <v>1360.932975467714</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S9" t="n">
-        <v>1297.853320462484</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T9" t="n">
-        <v>1293.343447077155</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U9" t="n">
-        <v>1120.665926755083</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V9" t="n">
-        <v>1106.008687167689</v>
+        <v>769.1063283981898</v>
       </c>
       <c r="W9" t="n">
-        <v>1073.308542814326</v>
+        <v>391.328550620412</v>
       </c>
       <c r="X9" t="n">
-        <v>1053.245169637167</v>
+        <v>29.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>1053.245169637167</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>947.812220936876</v>
+        <v>772.2280839062603</v>
       </c>
       <c r="C10" t="n">
-        <v>1073.814226755312</v>
+        <v>898.2300897246961</v>
       </c>
       <c r="D10" t="n">
-        <v>1187.133370880312</v>
+        <v>1011.549233849696</v>
       </c>
       <c r="E10" t="n">
-        <v>1304.962275091725</v>
+        <v>1129.378138061109</v>
       </c>
       <c r="F10" t="n">
-        <v>1381.441257449721</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="G10" t="n">
-        <v>1381.441257449721</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="H10" t="n">
-        <v>1381.441257449721</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="I10" t="n">
-        <v>1381.441257449721</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="J10" t="n">
-        <v>1381.441257449721</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="K10" t="n">
-        <v>1381.441257449721</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
         <v>1385.467095409585</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7813496506081</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>465.3425721249604</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>664.1639650109064</v>
+        <v>226.1397362770649</v>
       </c>
       <c r="W10" t="n">
-        <v>836.0548832705838</v>
+        <v>398.0306545367423</v>
       </c>
       <c r="X10" t="n">
-        <v>836.0548832705838</v>
+        <v>549.0614455609358</v>
       </c>
       <c r="Y10" t="n">
-        <v>836.0548832705838</v>
+        <v>660.4707462399681</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C11" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D11" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E11" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F11" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
         <v>125.5027119537179</v>
@@ -5032,16 +5032,16 @@
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K11" t="n">
-        <v>737.2059437357115</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L11" t="n">
-        <v>953.2578922784251</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M11" t="n">
-        <v>1595.767892278425</v>
+        <v>2060.500475851726</v>
       </c>
       <c r="N11" t="n">
         <v>2238.277892278425</v>
@@ -5065,19 +5065,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1316.525394051095</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C12" t="n">
-        <v>1100.675163417264</v>
+        <v>872.355231874462</v>
       </c>
       <c r="D12" t="n">
-        <v>749.2229544296858</v>
+        <v>845.1454471293079</v>
       </c>
       <c r="E12" t="n">
-        <v>403.0895228924003</v>
+        <v>823.2544398344467</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>480.1875283820457</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>151.9050926782826</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1525.215274341931</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095642</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V12" t="n">
-        <v>1672.26663826087</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W12" t="n">
-        <v>1559.768514109528</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X12" t="n">
-        <v>1459.907161134389</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y12" t="n">
-        <v>1380.723936118092</v>
+        <v>977.0587360076396</v>
       </c>
     </row>
     <row r="13">
@@ -5211,7 +5211,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
         <v>82.79157247680381</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C14" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D14" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E14" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G14" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H14" t="n">
         <v>51.92</v>
@@ -5269,22 +5269,22 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L14" t="n">
-        <v>949.6332762537361</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M14" t="n">
-        <v>1009.32297330616</v>
+        <v>523.631587033441</v>
       </c>
       <c r="N14" t="n">
-        <v>1651.83297330616</v>
+        <v>724.5350810277346</v>
       </c>
       <c r="O14" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P14" t="n">
         <v>2009.555081027735</v>
@@ -5293,28 +5293,28 @@
         <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X14" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="15">
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>816.937701241021</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C15" t="n">
-        <v>776.43273917484</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D15" t="n">
-        <v>749.2229544296858</v>
+        <v>1248.810647239759</v>
       </c>
       <c r="E15" t="n">
-        <v>403.0895228924003</v>
+        <v>920.9187291481937</v>
       </c>
       <c r="F15" t="n">
-        <v>60.0226114399994</v>
+        <v>577.8518176957928</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866058</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I15" t="n">
         <v>51.92</v>
@@ -5378,22 +5378,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
-        <v>1267.13416483617</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V15" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X15" t="n">
-        <v>960.3194683243149</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y15" t="n">
-        <v>881.1362433080176</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="16">
@@ -5439,19 +5439,19 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O16" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G17" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L17" t="n">
-        <v>1418.446838088717</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M17" t="n">
-        <v>1595.767892278425</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N17" t="n">
-        <v>2238.277892278425</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O17" t="n">
-        <v>2399.40799366138</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>343.7981213238219</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C18" t="n">
-        <v>303.2931592576408</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D18" t="n">
-        <v>276.0833745124866</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E18" t="n">
-        <v>254.1923672176254</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
-        <v>235.3678800076488</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G18" t="n">
-        <v>231.3278685463099</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H18" t="n">
-        <v>227.2652685676493</v>
+        <v>51.92</v>
       </c>
       <c r="I18" t="n">
         <v>51.92</v>
@@ -5615,22 +5615,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T18" t="n">
-        <v>1846.683151095641</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U18" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V18" t="n">
-        <v>1348.024214018445</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W18" t="n">
-        <v>1235.526089867103</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X18" t="n">
-        <v>811.4223126495401</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y18" t="n">
-        <v>407.9966633908185</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="19">
@@ -5682,13 +5682,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5758,10 +5758,10 @@
         <v>1808.651587033441</v>
       </c>
       <c r="O20" t="n">
-        <v>1969.781688416396</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P20" t="n">
-        <v>2166.373694755016</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.4528527561725</v>
+        <v>588.6177696982188</v>
       </c>
       <c r="C21" t="n">
-        <v>127.9478906899915</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D21" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E21" t="n">
         <v>78.84709864997603</v>
@@ -5843,31 +5843,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R21" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S21" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U21" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V21" t="n">
-        <v>1496.92136969322</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W21" t="n">
-        <v>1060.180821299454</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X21" t="n">
-        <v>636.0770440818908</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.6513948231691</v>
+        <v>652.8163117652153</v>
       </c>
     </row>
     <row r="22">
@@ -5916,16 +5916,16 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O22" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q22" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R22" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
@@ -5983,22 +5983,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L23" t="n">
-        <v>950.0896384907273</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M23" t="n">
-        <v>1592.599638490728</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N23" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O23" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P23" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6016,16 +6016,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W23" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>492.6952769985968</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424898</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>600.3257987549114</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>254.1923672176259</v>
       </c>
       <c r="F24" t="n">
-        <v>60.02261143999941</v>
+        <v>235.3678800076492</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6083,28 +6083,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R24" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S24" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U24" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V24" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W24" t="n">
-        <v>1384.423245541878</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X24" t="n">
-        <v>960.3194683243149</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y24" t="n">
-        <v>881.1362433080176</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="25">
@@ -6147,10 +6147,10 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O25" t="n">
         <v>1115.142339091088</v>
@@ -6159,7 +6159,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q25" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R25" t="n">
         <v>82.79157247680381</v>
@@ -6193,40 +6193,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H26" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L26" t="n">
-        <v>991.9887866314309</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M26" t="n">
-        <v>1634.498786631431</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N26" t="n">
         <v>2238.277892278425</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>816.937701241021</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C27" t="n">
-        <v>776.43273917484</v>
+        <v>1196.597656116886</v>
       </c>
       <c r="D27" t="n">
-        <v>749.2229544296858</v>
+        <v>1169.387871371732</v>
       </c>
       <c r="E27" t="n">
-        <v>727.3319471348246</v>
+        <v>823.2544398344464</v>
       </c>
       <c r="F27" t="n">
-        <v>384.2650356824237</v>
+        <v>480.1875283820455</v>
       </c>
       <c r="G27" t="n">
-        <v>380.2250242210849</v>
+        <v>151.9050926782824</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6317,31 +6317,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R27" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S27" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V27" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W27" t="n">
-        <v>1559.768514109528</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X27" t="n">
-        <v>1284.561892566739</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y27" t="n">
-        <v>881.1362433080176</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="28">
@@ -6381,7 +6381,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
         <v>1506.07469544798</v>
@@ -6442,7 +6442,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G29" t="n">
         <v>125.5027119537179</v>
@@ -6460,19 +6460,19 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L29" t="n">
-        <v>1418.446838088717</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M29" t="n">
-        <v>1418.446838088717</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N29" t="n">
-        <v>1792.359898617045</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O29" t="n">
-        <v>1953.49</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>992.2829698086708</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C30" t="n">
-        <v>951.7780077424898</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D30" t="n">
-        <v>924.5682229973356</v>
+        <v>1073.46537867211</v>
       </c>
       <c r="E30" t="n">
-        <v>578.4347914600501</v>
+        <v>727.3319471348245</v>
       </c>
       <c r="F30" t="n">
-        <v>235.3678800076491</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G30" t="n">
-        <v>231.3278685463103</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6554,31 +6554,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R30" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S30" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U30" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V30" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W30" t="n">
-        <v>1235.526089867104</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X30" t="n">
-        <v>1135.664736891965</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y30" t="n">
-        <v>1056.481511875667</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="31">
@@ -6618,22 +6618,22 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M31" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N31" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O31" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6694,49 +6694,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L32" t="n">
-        <v>950.0896384907273</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M32" t="n">
-        <v>1592.599638490728</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N32" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O32" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P32" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>343.7981213238222</v>
+        <v>816.9377012410209</v>
       </c>
       <c r="C33" t="n">
-        <v>303.293159257641</v>
+        <v>776.4327391748399</v>
       </c>
       <c r="D33" t="n">
-        <v>276.0833745124868</v>
+        <v>749.2229544296857</v>
       </c>
       <c r="E33" t="n">
-        <v>254.1923672176256</v>
+        <v>727.3319471348245</v>
       </c>
       <c r="F33" t="n">
-        <v>235.367880007649</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G33" t="n">
-        <v>231.3278685463101</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H33" t="n">
-        <v>227.2652685676496</v>
+        <v>51.92</v>
       </c>
       <c r="I33" t="n">
         <v>51.92</v>
@@ -6791,31 +6791,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q33" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R33" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S33" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884733</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095642</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V33" t="n">
-        <v>1348.024214018445</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W33" t="n">
-        <v>911.2836656246793</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X33" t="n">
-        <v>487.1798884071161</v>
+        <v>960.3194683243148</v>
       </c>
       <c r="Y33" t="n">
-        <v>407.9966633908188</v>
+        <v>881.1362433080175</v>
       </c>
     </row>
     <row r="34">
@@ -6867,13 +6867,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6937,10 +6937,10 @@
         <v>523.631587033441</v>
       </c>
       <c r="M35" t="n">
-        <v>1009.32297330616</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N35" t="n">
-        <v>1651.83297330616</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="O35" t="n">
         <v>1812.963074689115</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1316.525394051095</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C36" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D36" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E36" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F36" t="n">
         <v>60.02261143999941</v>
@@ -7031,28 +7031,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S36" t="n">
-        <v>1928.880474452383</v>
+        <v>1280.395625967535</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095642</v>
+        <v>1198.198302610793</v>
       </c>
       <c r="U36" t="n">
-        <v>1766.721857646244</v>
+        <v>942.8917405937455</v>
       </c>
       <c r="V36" t="n">
-        <v>1672.26663826087</v>
+        <v>524.1940969659473</v>
       </c>
       <c r="W36" t="n">
-        <v>1559.768514109528</v>
+        <v>411.6959728146054</v>
       </c>
       <c r="X36" t="n">
-        <v>1459.907161134389</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y36" t="n">
-        <v>1380.723936118092</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="37">
@@ -7165,25 +7165,25 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L38" t="n">
-        <v>950.0896384907273</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.599638490728</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N38" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O38" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P38" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1316.525394051095</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C39" t="n">
-        <v>1100.675163417264</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D39" t="n">
-        <v>749.2229544296858</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E39" t="n">
         <v>403.0895228924003</v>
@@ -7265,31 +7265,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q39" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R39" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S39" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.683151095642</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U39" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V39" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X39" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y39" t="n">
-        <v>1380.723936118092</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="40">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7405,22 +7405,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>307.5796384907274</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L41" t="n">
-        <v>523.631587033441</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M41" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N41" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O41" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P41" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7438,16 +7438,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7469,10 +7469,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F42" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7502,25 +7502,25 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1982.60944240224</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S42" t="n">
-        <v>1849.457698584356</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T42" t="n">
-        <v>1767.260375227614</v>
+        <v>1198.198302610793</v>
       </c>
       <c r="U42" t="n">
-        <v>1591.376589078594</v>
+        <v>942.8917405937455</v>
       </c>
       <c r="V42" t="n">
-        <v>1172.678945450796</v>
+        <v>524.1940969659473</v>
       </c>
       <c r="W42" t="n">
-        <v>735.9383970570298</v>
+        <v>411.6959728146054</v>
       </c>
       <c r="X42" t="n">
         <v>311.8346198394665</v>
@@ -7566,25 +7566,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L43" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N43" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O43" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R43" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D44" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H44" t="n">
         <v>51.92</v>
@@ -7639,52 +7639,52 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L44" t="n">
-        <v>950.0896384907273</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M44" t="n">
-        <v>1592.599638490728</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N44" t="n">
-        <v>2235.109638490728</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O44" t="n">
-        <v>2396.239739873683</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P44" t="n">
-        <v>2592.831746212303</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S44" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W44" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>686.2820590119658</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C45" t="n">
-        <v>645.7770969457847</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D45" t="n">
-        <v>618.5673122006306</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E45" t="n">
-        <v>596.6763049057694</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F45" t="n">
-        <v>577.8518176957928</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G45" t="n">
-        <v>573.8118062344539</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H45" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7745,25 +7745,25 @@
         <v>1737.789794027844</v>
       </c>
       <c r="S45" t="n">
-        <v>1298.637139413254</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T45" t="n">
-        <v>1216.439816056512</v>
+        <v>1347.095458285567</v>
       </c>
       <c r="U45" t="n">
-        <v>1136.478522607115</v>
+        <v>942.8917405937455</v>
       </c>
       <c r="V45" t="n">
-        <v>1042.023303221741</v>
+        <v>848.4365212083716</v>
       </c>
       <c r="W45" t="n">
-        <v>929.5251790703986</v>
+        <v>735.9383970570296</v>
       </c>
       <c r="X45" t="n">
-        <v>829.6638260952597</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y45" t="n">
-        <v>750.4806010789623</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="46">
@@ -7815,13 +7815,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7967,7 +7967,7 @@
         <v>372.8993027275024</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>320.3286984924623</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>844.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>776.3653500296342</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
         <v>0.4816735941929551</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>308.7655548853994</v>
+        <v>361.4368563929372</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>384.3316744713793</v>
+        <v>384.3316744713784</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>181.5167089435048</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>845.554996989051</v>
+        <v>705.843704712591</v>
       </c>
       <c r="N5" t="n">
-        <v>777.3653500296342</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
         <v>0.4816735941929551</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
-        <v>181.5167089435048</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>845.554996989051</v>
+        <v>771.1871117477669</v>
       </c>
       <c r="N8" t="n">
-        <v>777.3653500296342</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
         <v>0.4816735941929551</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.1077446289929</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>433.9659648939233</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>950.4344291498551</v>
+        <v>950.434429149855</v>
       </c>
       <c r="N11" t="n">
-        <v>879.4920535472222</v>
+        <v>410.0652014529786</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8921,16 +8921,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>361.7270524351312</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>433.4248757636803</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>480.5466050990546</v>
+        <v>560.3048366155554</v>
       </c>
       <c r="N17" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9401,13 +9401,13 @@
         <v>879.4920535472222</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>433.9659648939237</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>457.4494331410071</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L23" t="n">
         <v>430.7657085427136</v>
@@ -9635,7 +9635,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,10 +9860,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>473.0880804020101</v>
+        <v>3.661228307766578</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>840.3699380391354</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10103,22 +10103,22 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>608.1820136768461</v>
+        <v>248.0013330166451</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L32" t="n">
         <v>430.7657085427136</v>
@@ -10346,7 +10346,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,13 +10580,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>792.031789021288</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>879.4920535472222</v>
+        <v>234.8470915832563</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>3.661228307766578</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>950.4344291498551</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,13 +11048,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>792.031789021288</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
         <v>879.4920535472222</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>950.4344291498551</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26.68372459829277</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.927393539208561</v>
+        <v>1.927393539209187</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8382458495976959</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23654,7 +23654,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24131,7 +24131,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24362,13 +24362,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24851,7 +24851,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -25088,10 +25088,10 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25781,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26036,10 +26036,10 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26281,7 +26281,7 @@
         <v>1416776.537736231</v>
       </c>
       <c r="F2" t="n">
-        <v>1416776.53773623</v>
+        <v>1416776.537736231</v>
       </c>
       <c r="G2" t="n">
         <v>1416776.537736231</v>
@@ -26308,7 +26308,7 @@
         <v>1416776.537736231</v>
       </c>
       <c r="O2" t="n">
-        <v>1416776.537736231</v>
+        <v>1416776.53773623</v>
       </c>
       <c r="P2" t="n">
         <v>1416776.537736231</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577307.7597977305</v>
+        <v>570823.1065049333</v>
       </c>
       <c r="C4" t="n">
-        <v>575232.1895180241</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573221.1009892204</v>
+        <v>566727.0147207876</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562992</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>549046.4124850022</v>
+        <v>555531.0657777996</v>
       </c>
       <c r="C6" t="n">
-        <v>782602.780856145</v>
+        <v>789096.867124578</v>
       </c>
       <c r="D6" t="n">
-        <v>784965.8693849489</v>
+        <v>791459.9556533817</v>
       </c>
       <c r="E6" t="n">
-        <v>264318.0089400561</v>
+        <v>270781.0000704098</v>
       </c>
       <c r="F6" t="n">
-        <v>854579.0717582781</v>
+        <v>861042.0628886326</v>
       </c>
       <c r="G6" t="n">
-        <v>856267.4612799314</v>
+        <v>862730.4524102859</v>
       </c>
       <c r="H6" t="n">
-        <v>857958.1941898944</v>
+        <v>864421.1853202486</v>
       </c>
       <c r="I6" t="n">
-        <v>859651.2873904415</v>
+        <v>866114.278520796</v>
       </c>
       <c r="J6" t="n">
-        <v>473250.7580053663</v>
+        <v>479713.7491357205</v>
       </c>
       <c r="K6" t="n">
-        <v>862692.6233842002</v>
+        <v>869155.614514554</v>
       </c>
       <c r="L6" t="n">
-        <v>864744.9011065437</v>
+        <v>871207.8922368977</v>
       </c>
       <c r="M6" t="n">
-        <v>769647.6089865115</v>
+        <v>776110.6001168655</v>
       </c>
       <c r="N6" t="n">
-        <v>868152.7650772755</v>
+        <v>874615.7562076292</v>
       </c>
       <c r="O6" t="n">
-        <v>613060.3876757371</v>
+        <v>619523.3788060911</v>
       </c>
       <c r="P6" t="n">
-        <v>871570.4953273209</v>
+        <v>878033.4864576751</v>
       </c>
     </row>
   </sheetData>
@@ -26975,10 +26975,10 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>321</v>
@@ -26999,10 +26999,10 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>399.9999999999994</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27521,19 +27521,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>302.4897051535225</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27569,16 +27569,16 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>285.7601180131394</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>41.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>46.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,16 +27591,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>393.7442253765199</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27609,7 +27609,7 @@
         <v>244.858135136612</v>
       </c>
       <c r="H4" t="n">
-        <v>324.747576689239</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
@@ -27654,7 +27654,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.0465935392085</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.56186855214403</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>159.5184388018133</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>292.0434297503306</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27834,7 +27834,7 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>294.3826718271959</v>
+        <v>335.2460937636845</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>222.9148456338345</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27992,16 +27992,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
         <v>330.0284079411381</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,16 +28043,16 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>229.2450391696371</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>62.06827433117968</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28077,7 +28077,7 @@
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>351.6343532990513</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>244.858135136612</v>
@@ -28092,10 +28092,10 @@
         <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28119,22 +28119,22 @@
         <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>397.3720640314333</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28159,7 +28159,7 @@
         <v>321</v>
       </c>
       <c r="G11" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="H11" t="n">
         <v>321</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28226,22 +28226,22 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="I12" t="n">
         <v>191.6509141932353</v>
@@ -28268,13 +28268,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28399,7 +28399,7 @@
         <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I14" t="n">
         <v>96.76634561233286</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28469,19 +28469,19 @@
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>18.05909831126257</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>321</v>
       </c>
       <c r="I15" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28514,10 +28514,10 @@
         <v>321</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28700,13 +28700,13 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
@@ -28718,7 +28718,7 @@
         <v>321</v>
       </c>
       <c r="I18" t="n">
-        <v>18.05909831126252</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28751,22 +28751,22 @@
         <v>321</v>
       </c>
       <c r="T18" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="U18" t="n">
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W18" t="n">
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28937,13 +28937,13 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="D21" t="n">
         <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -28994,7 +28994,7 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -29003,7 +29003,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29110,10 +29110,10 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29171,22 +29171,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>321</v>
       </c>
       <c r="G24" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="H24" t="n">
         <v>321</v>
@@ -29219,7 +29219,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>321</v>
@@ -29234,10 +29234,10 @@
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29417,16 +29417,16 @@
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>226.0367322273744</v>
       </c>
       <c r="I27" t="n">
         <v>191.6509141932353</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
@@ -29474,10 +29474,10 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29648,7 +29648,7 @@
         <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="D30" t="n">
         <v>321</v>
@@ -29663,7 +29663,7 @@
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>147.4081841180268</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>191.6509141932353</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29708,7 +29708,7 @@
         <v>321</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X30" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29894,16 +29894,16 @@
         <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>18.05909831126229</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,10 +29927,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>321</v>
+        <v>226.0367322273741</v>
       </c>
       <c r="S33" t="n">
         <v>321</v>
@@ -29945,10 +29945,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -30122,16 +30122,16 @@
         <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
@@ -30167,19 +30167,19 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>321</v>
       </c>
       <c r="U36" t="n">
-        <v>321</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="V36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>321</v>
@@ -30359,13 +30359,13 @@
         <v>321</v>
       </c>
       <c r="C39" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -30401,10 +30401,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="S39" t="n">
         <v>321</v>
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346856</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30638,28 +30638,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
       </c>
       <c r="T42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>226.0367322273742</v>
+        <v>147.4081841180264</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30769,7 +30769,7 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I44" t="n">
         <v>96.76634561233286</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30833,7 +30833,7 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>321</v>
@@ -30848,10 +30848,10 @@
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30881,13 +30881,13 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>18.05909831126212</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>321</v>
@@ -34746,16 +34746,16 @@
         <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>372.9999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517586</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M2" t="n">
         <v>373</v>
       </c>
       <c r="N2" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>180.6578102564064</v>
+        <v>233.3291117639442</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34828,7 +34828,7 @@
         <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>318.4376284546078</v>
+        <v>318.4376284546069</v>
       </c>
       <c r="M3" t="n">
         <v>143.0850421645043</v>
@@ -34877,16 +34877,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>106.6304250394412</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>97.62782763680069</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
         <v>228.952183724144</v>
@@ -34940,7 +34940,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>52.67130150753769</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>246.8601159786807</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
-        <v>374</v>
+        <v>234.2887077235401</v>
       </c>
       <c r="N5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35120,7 +35120,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>8.846453771640441</v>
+        <v>49.70987570812906</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.86342193648883</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>190.7690400511193</v>
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>246.8601159786807</v>
+        <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>299.6321147587159</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35363,7 +35363,7 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>77.25149733130939</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35378,10 +35378,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>4.066502989761812</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,22 +35405,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>198.2017538152171</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,10 +35454,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K11" t="n">
-        <v>609.8778844919133</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>218.2342914572864</v>
@@ -35466,7 +35466,7 @@
         <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>179.5731479057565</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35691,7 +35691,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
         <v>175.9119195979899</v>
@@ -35700,16 +35700,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
-        <v>60.29262328527617</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
+        <v>202.9328222164582</v>
+      </c>
+      <c r="O14" t="n">
         <v>649</v>
       </c>
-      <c r="O14" t="n">
-        <v>162.757678164601</v>
-      </c>
       <c r="P14" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q14" t="n">
         <v>592.3686050224903</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
-        <v>179.1121759491996</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P17" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36080,7 +36080,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H19" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I19" t="n">
         <v>163.0214951995539</v>
@@ -36180,13 +36180,13 @@
         <v>649</v>
       </c>
       <c r="O20" t="n">
-        <v>162.757678164601</v>
+        <v>596.7236430585247</v>
       </c>
       <c r="P20" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>433.9659648939237</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36405,7 +36405,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L23" t="n">
         <v>649</v>
@@ -36414,7 +36414,7 @@
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
@@ -36423,7 +36423,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36639,10 +36639,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>649</v>
+        <v>179.5731479057565</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
@@ -36651,7 +36651,7 @@
         <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36882,22 +36882,22 @@
         <v>649</v>
       </c>
       <c r="L29" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M29" t="n">
         <v>649</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
-        <v>377.6899601296238</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37116,7 +37116,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L32" t="n">
         <v>649</v>
@@ -37125,7 +37125,7 @@
         <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37359,13 +37359,13 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M35" t="n">
-        <v>490.597359871433</v>
+        <v>649</v>
       </c>
       <c r="N35" t="n">
+        <v>4.355038036034114</v>
+      </c>
+      <c r="O35" t="n">
         <v>649</v>
-      </c>
-      <c r="O35" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
         <v>198.5777841804241</v>
@@ -37587,13 +37587,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
-        <v>175.9119195979899</v>
+        <v>179.5731479057565</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
         <v>649</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37827,13 +37827,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
-        <v>490.597359871433</v>
+        <v>649</v>
       </c>
       <c r="N41" t="n">
         <v>649</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
         <v>649</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.200256351209361</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
@@ -38264,7 +38264,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y46" t="n">
-        <v>33.53464715053765</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
   </sheetData>
